--- a/data/Human validated 50 questions.xlsx
+++ b/data/Human validated 50 questions.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="1" min="1" max="1"/>
@@ -656,10 +656,10 @@
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>There are 4 Thermal Management companies in Georgia.
-  • Freudenberg-NOK | OEMs: Multiple OEMs
-  • Hyundai Transys Georgia Powertrain | OEMs: Hyundai Kia Rivian
-  • Novelis Inc. | OEMs: Multiple OEMs
-  • Peerless-Winsmith Inc. | OEMs: Multiple OEMs</t>
+• Freudenberg-NOK | Location: LaGrange, Troup County | OEMs: Multiple OEMs
+• Hyundai Transys Georgia Powertrain | Location: West Point, Troup County | OEMs: Hyundai Kia Rivian
+• Novelis Inc. | Location: Atlanta, Fulton County | OEMs: Multiple OEMs
+• Peerless-Winsmith Inc. | Location: Flowery Branch, Hall County | OEMs: Multiple OEMs</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,11 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Novelis Inc. is recorded at three Georgia locations.
-Gainesville, Hall County | Primary Facility Type: Manufacturing Plant
-Trenton, Dade County | Primary Facility Type: Manufacturing Plant
-Lawrenceville, Gwinnett County | Primary Facility Type: Manufacturing Plant</t>
+          <t>Novelis Inc. has 3 facility records in Georgia, all updated to the same location.
+Atlanta, Fulton County | Primary Facility Type: Manufacturing Plant
+Atlanta, Fulton County | Primary Facility Type: Manufacturing Plant
+Atlanta, Fulton County | Primary Facility Type: Manufacturing Plant
+Note: The original Location column showed entries for Dalton and Atlanta; the Updated Location column consolidates all three records to Atlanta, Fulton County.</t>
         </is>
       </c>
     </row>
@@ -757,8 +758,10 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Highest-employment company in Gwinnett County:
-Grudem | Employment: 807 | EV Supply Chain Role: General Automotive</t>
+          <t>In Gwinnett County, per the data record, WIKA USA has the highest reported employment figure at 250,000; however this reflects global corporate headcount rather than local Georgia employment.
+Excluding the global-headcount outlier, the highest locally-reported employment in Gwinnett County is:
+SungEel Recycling Park Georgia | Employment: 650 | Updated Location: Duluth, Gwinnett County | EV Supply Chain Role: Materials
+Note: Grudem (807 employees, General Automotive, Gainesville, Hall County) is recorded under Hall County in the Updated Location column, not Gwinnett County.</t>
         </is>
       </c>
     </row>
@@ -778,7 +781,13 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Troup County has the highest total employment among Tier 1 suppliers, with 3,603 employees.</t>
+          <t>Troup County has the highest total employment among automotive supply chain participants (non-OEM), with approximately 3,330 employees across its Updated Location entries.
+Top counties by supply chain participant employment (excluding global headcount outliers &gt;100,000):
+Troup County:       3,330
+Gwinnett County:    3,022
+Forsyth County:     2,080
+Laurens County:     1,943
+Harris County:      1,903</t>
         </is>
       </c>
     </row>
@@ -798,7 +807,14 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Fulton County | Total Employment: 21,300</t>
+          <t>Laurens County | Total Employment: 88,943 (all companies, Updated Location, excluding companies reporting &gt;100,000 which represent global headcount)
+Top counties by total employment:
+Laurens County:   88,943
+Bartow County:    23,030
+Forsyth County:   21,680
+Jackson County:   19,723
+Hall County:      19,307
+Note: The previous answer of Fulton County (21,300) was based on the original Location column. Using the Updated Location column, Laurens County ranks highest due to large employers including ZF, IMMI, and others headquartered in the Dublin area.</t>
         </is>
       </c>
     </row>
@@ -853,10 +869,11 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Sewon America Inc. offers different products and services across its Georgia locations
-Atlanta, Fulton County: Automotive aftermarket parts
-Athens, Clarke County: Motor vehicle engines and parts
-Marietta, Cobb County: Fire truck bodies</t>
+          <t>Sewon America Inc. offers different products and services across its Georgia facilities. Per the Updated Location column, all three records are located in:
+LaGrange, Troup County | Product: Motor vehicle engines and parts
+LaGrange, Troup County | Product: Fire truck bodies
+LaGrange, Troup County | Product: Automotive aftermarket parts
+Note: The original Location column showed entries for Peachtree City (Chattooga County), West Point (Troup County), and Gray (Jones County). The Updated Location consolidates all three to LaGrange, Troup County.</t>
         </is>
       </c>
     </row>
@@ -951,10 +968,10 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">There are 3 Georgia companies with products or roles related to wiring harnesses. 
-Solvay Specialty Polymers USA LLC | Primary OEMs: Multiple OEMs
-WIKA USA | Primary OEMs: not listed 
-Woodbridge Foam Corp. | Primary OEMs: not listed </t>
+          <t>There are 2 Georgia companies with EV Supply Chain Roles explicitly related to wiring harnesses.
+WIKA USA | Role: HV and LV wiring harnesses for EVs and ICE vehicles | Location: Lawrenceville, Gwinnett County | Primary OEMs: not listed
+Woodbridge Foam Corp. | Role: EV wiring harnesses and power distribution | Location: Lithonia, DeKalb County | Primary OEMs: not listed
+Note: Solvay Specialty Polymers USA LLC was removed from this answer — its EV Supply Chain Role is classified as General Automotive, not wiring harnesses.</t>
         </is>
       </c>
     </row>
@@ -1560,10 +1577,10 @@
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>There are 3 Georgia automotive companies employ more than 1,000 workers while being categorized as Indirectly Relevant to the EV sector:
-TCI Powder Coatings: 1,200 employees
-Teklas USA: 1,300 employees
-Textron Specialized Vehicles: 1,225 employees</t>
+          <t>There are 3 Georgia automotive companies that employ more than 1,000 workers while being categorised as Indirectly Relevant to the EV sector:
+TCI Powder Coatings | Employment: 3,000 | Updated Location: Ellaville, Schley County
+Teklas USA | Employment: 1,800 | Updated Location: Calhoun, Gordon County
+Textron Specialized Vehicles | Employment: 1,100 | Updated Location: Augusta, Richmond County</t>
         </is>
       </c>
     </row>
@@ -1807,25 +1824,30 @@
       </c>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>There are 22 Materials companies distributed across 18 areas in the Georgia automotive ecosystem. Below are the Georgia counties and locations with the count of Materials companies in each area:
-Troup County: 2 
-Gainesville, Hall County: 2 
-Augusta, Richmond County: 2 
-Cartersville, Bartow County: 2 
-Statesboro, Bulloch County: 1 
+          <t>There are 22 Materials companies distributed across 21 areas in the Georgia automotive ecosystem. Using Updated Location, the areas with the highest concentration of Materials companies are:
+Covington, Henry County: 2
+All other areas have 1 each:
+Bloomingdale, Chatham County: 1
+Blue Ridge, Union County: 1
+Buford, Hall County: 1
+Augusta, Richmond County: 1
+Calhoun, Gordon County: 1
+Cartersville, Bartow County: 1
+Duluth, Gwinnett County: 1
+Ellabell, Bryan County: 1
+Evans, Columbia County: 1
+Fort Valley, Peach County: 1
 Griffin, Spalding County: 1
-Elberton, Elbert County: 1
-Canton, Cherokee County: 1 
-Thomson, McDuffie County: 1
-Madison, Morgan County: 1
-Covington, Newton County: 1
-Marietta, Cobb County: 1
-Cumming, Forsyth County: 1
-Albany, Dougherty County: 1
-Dahlonega, Lumpkin County: 1
-Carroll County: 1
-Hartwell, Hart County: 1
-Macon, Bibb County: 1</t>
+Lavonia, Franklin County: 1
+Mableton, Cobb County: 1
+Macon, Bibb County: 1
+Mansfield, Newton County: 1
+Metter, Candler County: 1
+Peachtree City, Fayette County: 1
+Smyrna, Cobb County: 1
+Statesboro: 1
+Toccoa, Stephens County: 1
+For a new Tier 1 battery thermal management company, Covington (Henry County) is the single area with the highest density (2 Materials suppliers).</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1867,32 @@
       </c>
       <c r="D49" s="21" t="inlineStr">
         <is>
-          <t>There are 82 non-EV Manufacturing Plant companies distributed across 22 Georgia areas with concentrated Manufacturing Plant facilities but no EV-specific production presence. The areas and counts are:
-Troup County: 12
-Lawrenceville, Gwinnett County: 4
-Gainesville, Hall County: 4
-Rome, Floyd County: 4
-Dalton, Whitfield County: 3
-Statesboro, Bulloch County: 3
-Atlanta, Fulton County: 3
-Buchanan, Haralson County: 2
-Calhoun, Gordon County: 2
-Hinesville, Liberty County: 2
-Covington, Newton County: 2
-Coweta County: 2
-Griffin, Spalding County: 2
-Hazlehurst, Davis County: 2
-Trenton, Dade County: 2
-Augusta, Richmond County: 2
-Cumming, Forsyth County: 2
-Carroll County: 2
-Marietta, Cobb County: 2
-Fayetteville, Fayette County: 2
-Savannah, Chatham County: 2
-Cartersville, Bartow County: 2</t>
+          <t>There are 162 non-EV Manufacturing Plant company records distributed across 100 areas in Georgia (using Updated Location). The top areas by concentration are:
+LaGrange, Troup County: 7
+Atlanta, Fulton County: 6
+West Point, Troup County: 6
+Dublin, Laurens County: 4
+Savannah, Chatham County: 4
+Griffin, Spalding County: 3
+Madison, Morgan County: 3
+Lavonia, Franklin County: 3
+Duluth, Gwinnett County: 3
+Jefferson, Jackson County: 3
+Augusta, Richmond County: 3
+Suwanee, Gwinnett County: 3
+Covington, Newton County: 3
+Dawsonville, Dawson County: 2
+Alpharetta, Forsyth County: 2
+Commerce, Forsyth County: 2
+Covington, Henry County: 2
+Carrollton, Carroll County: 2
+Buford, Hall County: 2
+Athens, Clarke County: 2
+Ellabell, Chatham County: 2
+Flowery Branch, Hall County: 2
+Gainesville, Hall County: 2
+Hogansville, Meriwether County: 2
+Macon, Bibb County: 2</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1935,8 @@
       <c r="D51" s="21" t="inlineStr">
         <is>
           <t>There is only 1 Georgia area with an R&amp;D facility type in the automotive sector:
-Calhoun, Gordon County | Company: Racemark International LLC</t>
+Gray, Jones County | Company: Racemark International LLC | Product: Manufacturing and R&amp;D engine parts for EV
+Note: The original Location column showed this company in Atlanta (Fulton County) and Calhoun (Gordon County). The Updated Location column places Racemark International LLC in Gray, Jones County.</t>
         </is>
       </c>
     </row>
